--- a/artfynd/A 44409-2026 artfynd.xlsx
+++ b/artfynd/A 44409-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137282833</v>
       </c>
       <c r="B3" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137282834</v>
       </c>
       <c r="B4" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>137282835</v>
       </c>
       <c r="B5" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
